--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ57"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1746,38 +1746,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134372167</v>
+        <v>136991757</v>
       </c>
       <c r="B11" t="n">
-        <v>58131</v>
+        <v>58169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524266</v>
+        <v>524075</v>
       </c>
       <c r="R11" t="n">
-        <v>6713775</v>
+        <v>6713944</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,22 +1816,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,16 +1857,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134372167</t>
+          <t>https://artportalen.se/Sighting/136991757</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134372414</v>
+        <v>134372167</v>
       </c>
       <c r="B12" t="n">
-        <v>58658</v>
+        <v>58131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,16 +1874,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103023</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1899,14 +1899,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524201</v>
+        <v>524266</v>
       </c>
       <c r="R12" t="n">
-        <v>6713748</v>
+        <v>6713775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,16 +1974,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134372414</t>
+          <t>https://artportalen.se/Sighting/134372167</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524063</v>
+        <v>134372414</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>58658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,34 +1991,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524262</v>
+        <v>524201</v>
       </c>
       <c r="R13" t="n">
-        <v>6713854</v>
+        <v>6713748</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,22 +2050,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,13 +2091,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123524063</t>
+          <t>https://artportalen.se/Sighting/134372414</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524517</v>
+        <v>123524063</v>
       </c>
       <c r="B14" t="n">
         <v>8455</v>
@@ -2127,10 +2132,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524209</v>
+        <v>524262</v>
       </c>
       <c r="R14" t="n">
-        <v>6713935</v>
+        <v>6713854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2177,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,13 +2203,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123524517</t>
+          <t>https://artportalen.se/Sighting/123524063</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128218294</v>
+        <v>123524517</v>
       </c>
       <c r="B15" t="n">
         <v>8455</v>
@@ -2233,21 +2238,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524305</v>
+        <v>524209</v>
       </c>
       <c r="R15" t="n">
-        <v>6713475</v>
+        <v>6713935</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,22 +2274,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2315,70 +2315,56 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128218294</t>
+          <t>https://artportalen.se/Sighting/123524517</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122915193</v>
+        <v>128218294</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524288</v>
+        <v>524305</v>
       </c>
       <c r="R16" t="n">
-        <v>6713811</v>
+        <v>6713475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,27 +2391,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Under en äldre gran, 2 överblommade från förra året.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,13 +2432,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122915193</t>
+          <t>https://artportalen.se/Sighting/128218294</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122916997</v>
+        <v>122915193</v>
       </c>
       <c r="B17" t="n">
         <v>99118</v>
@@ -2507,14 +2488,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524142</v>
+        <v>524288</v>
       </c>
       <c r="R17" t="n">
-        <v>6713729</v>
+        <v>6713811</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2546,7 +2527,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2556,12 +2537,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>Under en äldre gran, 2 överblommade från förra året.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2587,13 +2568,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122916997</t>
+          <t>https://artportalen.se/Sighting/122915193</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B18" t="n">
         <v>99118</v>
@@ -2623,12 +2604,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2647,7 +2628,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R18" t="n">
         <v>6713729</v>
@@ -2682,7 +2663,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2692,12 +2673,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,13 +2704,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122917069</t>
+          <t>https://artportalen.se/Sighting/122916997</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122957710</v>
+        <v>122917069</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2759,7 +2740,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2772,16 +2753,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524145</v>
+        <v>524154</v>
       </c>
       <c r="R19" t="n">
-        <v>6713733</v>
+        <v>6713729</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2808,27 +2794,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,13 +2840,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122957710</t>
+          <t>https://artportalen.se/Sighting/122917069</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122958064</v>
+        <v>122957710</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2890,12 +2876,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2903,21 +2889,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524144</v>
+        <v>524145</v>
       </c>
       <c r="R20" t="n">
-        <v>6713722</v>
+        <v>6713733</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2949,7 +2930,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2959,12 +2940,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2990,13 +2971,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958064</t>
+          <t>https://artportalen.se/Sighting/122957710</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122958244</v>
+        <v>122958064</v>
       </c>
       <c r="B21" t="n">
         <v>99118</v>
@@ -3026,12 +3007,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3050,10 +3031,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524143</v>
+        <v>524144</v>
       </c>
       <c r="R21" t="n">
-        <v>6713721</v>
+        <v>6713722</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3085,7 +3066,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3095,12 +3076,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3126,13 +3107,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958244</t>
+          <t>https://artportalen.se/Sighting/122958064</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122958484</v>
+        <v>122958244</v>
       </c>
       <c r="B22" t="n">
         <v>99118</v>
@@ -3162,7 +3143,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3186,10 +3167,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524142</v>
+        <v>524143</v>
       </c>
       <c r="R22" t="n">
-        <v>6713723</v>
+        <v>6713721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3221,7 +3202,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3231,7 +3212,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3257,13 +3243,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958484</t>
+          <t>https://artportalen.se/Sighting/122958244</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122958550</v>
+        <v>122958484</v>
       </c>
       <c r="B23" t="n">
         <v>99118</v>
@@ -3293,7 +3279,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3317,10 +3303,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524147</v>
+        <v>524142</v>
       </c>
       <c r="R23" t="n">
-        <v>6713728</v>
+        <v>6713723</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3338,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3362,12 +3348,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3393,13 +3374,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958550</t>
+          <t>https://artportalen.se/Sighting/122958484</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122958631</v>
+        <v>122958550</v>
       </c>
       <c r="B24" t="n">
         <v>99118</v>
@@ -3429,7 +3410,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3453,10 +3434,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524136</v>
+        <v>524147</v>
       </c>
       <c r="R24" t="n">
-        <v>6713723</v>
+        <v>6713728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3488,7 +3469,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3498,12 +3479,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3529,13 +3510,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958631</t>
+          <t>https://artportalen.se/Sighting/122958550</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123310872</v>
+        <v>122958631</v>
       </c>
       <c r="B25" t="n">
         <v>99118</v>
@@ -3565,12 +3546,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3578,16 +3559,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524248</v>
+        <v>524136</v>
       </c>
       <c r="R25" t="n">
-        <v>6713835</v>
+        <v>6713723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3614,22 +3600,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3655,13 +3646,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123310872</t>
+          <t>https://artportalen.se/Sighting/122958631</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123311027</v>
+        <v>123310872</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3691,12 +3682,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3704,21 +3695,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524271</v>
+        <v>524248</v>
       </c>
       <c r="R26" t="n">
-        <v>6713818</v>
+        <v>6713835</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3750,7 +3736,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3760,7 +3746,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3786,13 +3772,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123311027</t>
+          <t>https://artportalen.se/Sighting/123310872</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123311089</v>
+        <v>123311027</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3822,7 +3808,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3846,10 +3832,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524298</v>
+        <v>524271</v>
       </c>
       <c r="R27" t="n">
-        <v>6713774</v>
+        <v>6713818</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,7 +3867,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3891,7 +3877,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3917,13 +3903,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123311089</t>
+          <t>https://artportalen.se/Sighting/123311027</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123311251</v>
+        <v>123311089</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3977,10 +3963,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524319</v>
+        <v>524298</v>
       </c>
       <c r="R28" t="n">
-        <v>6713759</v>
+        <v>6713774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4012,7 +3998,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4022,7 +4008,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4048,13 +4034,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123311251</t>
+          <t>https://artportalen.se/Sighting/123311089</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123359713</v>
+        <v>123311251</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -4084,7 +4070,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4097,16 +4083,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524277</v>
+        <v>524319</v>
       </c>
       <c r="R29" t="n">
-        <v>6713805</v>
+        <v>6713759</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4133,22 +4124,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4174,13 +4165,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123359713</t>
+          <t>https://artportalen.se/Sighting/123311251</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123360098</v>
+        <v>123359713</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -4229,10 +4220,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524214</v>
+        <v>524277</v>
       </c>
       <c r="R30" t="n">
-        <v>6713889</v>
+        <v>6713805</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4264,7 +4255,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4265,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4300,13 +4291,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123360098</t>
+          <t>https://artportalen.se/Sighting/123359713</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123411453</v>
+        <v>123360098</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -4336,12 +4327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4349,21 +4340,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524217</v>
+        <v>524214</v>
       </c>
       <c r="R31" t="n">
-        <v>6713890</v>
+        <v>6713889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4390,27 +4376,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>10-20 bladrosetter.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4436,13 +4417,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123411453</t>
+          <t>https://artportalen.se/Sighting/123360098</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123523873</v>
+        <v>123411453</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -4472,7 +4453,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4496,10 +4477,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524302</v>
+        <v>524217</v>
       </c>
       <c r="R32" t="n">
-        <v>6713791</v>
+        <v>6713890</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4526,27 +4507,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+          <t>10-20 bladrosetter.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4572,13 +4553,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123523873</t>
+          <t>https://artportalen.se/Sighting/123411453</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123524367</v>
+        <v>123523873</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4608,7 +4589,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4621,16 +4602,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524214</v>
+        <v>524302</v>
       </c>
       <c r="R33" t="n">
-        <v>6713917</v>
+        <v>6713791</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4662,7 +4648,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4672,7 +4658,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4698,13 +4689,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123524367</t>
+          <t>https://artportalen.se/Sighting/123523873</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123524383</v>
+        <v>123524367</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4734,7 +4725,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4753,10 +4744,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524223</v>
+        <v>524214</v>
       </c>
       <c r="R34" t="n">
-        <v>6713905</v>
+        <v>6713917</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4788,7 +4779,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4798,7 +4789,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4824,13 +4815,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123524383</t>
+          <t>https://artportalen.se/Sighting/123524367</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123525488</v>
+        <v>123524383</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4860,12 +4851,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4873,21 +4864,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524128</v>
+        <v>524223</v>
       </c>
       <c r="R35" t="n">
-        <v>6714020</v>
+        <v>6713905</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4919,7 +4905,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4929,12 +4915,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4960,13 +4941,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123525488</t>
+          <t>https://artportalen.se/Sighting/123524383</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123526406</v>
+        <v>123525488</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4996,7 +4977,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5020,10 +5001,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524109</v>
+        <v>524128</v>
       </c>
       <c r="R36" t="n">
-        <v>6713892</v>
+        <v>6714020</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5055,7 +5036,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5065,12 +5046,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5096,13 +5077,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123526406</t>
+          <t>https://artportalen.se/Sighting/123525488</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123526470</v>
+        <v>123526406</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -5132,12 +5113,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5156,10 +5137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524101</v>
+        <v>524109</v>
       </c>
       <c r="R37" t="n">
-        <v>6713880</v>
+        <v>6713892</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5191,7 +5172,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5201,7 +5182,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5227,13 +5213,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123526470</t>
+          <t>https://artportalen.se/Sighting/123526406</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124432412</v>
+        <v>123526470</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -5263,7 +5249,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5276,16 +5262,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524183</v>
+        <v>524101</v>
       </c>
       <c r="R38" t="n">
-        <v>6713449</v>
+        <v>6713880</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5312,22 +5303,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5353,13 +5344,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124432412</t>
+          <t>https://artportalen.se/Sighting/123526470</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124591744</v>
+        <v>124432412</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -5389,7 +5380,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5402,21 +5393,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524311</v>
+        <v>524183</v>
       </c>
       <c r="R39" t="n">
-        <v>6713773</v>
+        <v>6713449</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5443,27 +5429,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5489,13 +5470,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124591744</t>
+          <t>https://artportalen.se/Sighting/124432412</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124591835</v>
+        <v>124591744</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5525,7 +5506,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5549,7 +5530,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524313</v>
+        <v>524311</v>
       </c>
       <c r="R40" t="n">
         <v>6713773</v>
@@ -5584,7 +5565,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5594,12 +5575,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5625,13 +5606,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124591835</t>
+          <t>https://artportalen.se/Sighting/124591744</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124591904</v>
+        <v>124591835</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5661,7 +5642,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5685,10 +5666,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524312</v>
+        <v>524313</v>
       </c>
       <c r="R41" t="n">
-        <v>6713764</v>
+        <v>6713773</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5720,7 +5701,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5730,7 +5711,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5756,13 +5742,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124591904</t>
+          <t>https://artportalen.se/Sighting/124591835</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124592554</v>
+        <v>124591904</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5792,17 +5778,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5812,14 +5798,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524359</v>
+        <v>524312</v>
       </c>
       <c r="R42" t="n">
-        <v>6713627</v>
+        <v>6713764</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5851,7 +5837,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5861,12 +5847,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:36</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5892,13 +5873,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124592554</t>
+          <t>https://artportalen.se/Sighting/124591904</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126932450</v>
+        <v>124592554</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5928,7 +5909,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5938,19 +5919,24 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524097</v>
+        <v>524359</v>
       </c>
       <c r="R43" t="n">
-        <v>6713893</v>
+        <v>6713627</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5977,22 +5963,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6018,13 +6009,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932450</t>
+          <t>https://artportalen.se/Sighting/124592554</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126932846</v>
+        <v>126932450</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -6054,7 +6045,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6069,14 +6060,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524149</v>
+        <v>524097</v>
       </c>
       <c r="R44" t="n">
-        <v>6713719</v>
+        <v>6713893</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,7 +6099,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6118,7 +6109,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6144,13 +6135,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932846</t>
+          <t>https://artportalen.se/Sighting/126932450</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126936299</v>
+        <v>126932846</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -6195,14 +6186,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524172</v>
+        <v>524149</v>
       </c>
       <c r="R45" t="n">
-        <v>6713431</v>
+        <v>6713719</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6234,7 +6225,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6244,7 +6235,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6270,13 +6261,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126936299</t>
+          <t>https://artportalen.se/Sighting/126932846</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126936747</v>
+        <v>126936299</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -6306,7 +6297,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6321,14 +6312,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524288</v>
+        <v>524172</v>
       </c>
       <c r="R46" t="n">
-        <v>6713820</v>
+        <v>6713431</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6360,7 +6351,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6370,7 +6361,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6396,13 +6387,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126936747</t>
+          <t>https://artportalen.se/Sighting/126936299</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126962144</v>
+        <v>126936747</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -6432,7 +6423,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6451,10 +6442,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524099</v>
+        <v>524288</v>
       </c>
       <c r="R47" t="n">
-        <v>6713924</v>
+        <v>6713820</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6481,22 +6472,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6522,13 +6513,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126962144</t>
+          <t>https://artportalen.se/Sighting/126936747</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126963918</v>
+        <v>126962144</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -6558,7 +6549,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6571,21 +6562,16 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524298</v>
+        <v>524099</v>
       </c>
       <c r="R48" t="n">
-        <v>6713794</v>
+        <v>6713924</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6617,7 +6603,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6627,7 +6613,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6653,13 +6639,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126963918</t>
+          <t>https://artportalen.se/Sighting/126962144</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126963963</v>
+        <v>126963918</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -6689,7 +6675,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6713,10 +6699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524305</v>
+        <v>524298</v>
       </c>
       <c r="R49" t="n">
-        <v>6713787</v>
+        <v>6713794</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6748,7 +6734,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6758,7 +6744,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6784,13 +6770,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126963963</t>
+          <t>https://artportalen.se/Sighting/126963918</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126964000</v>
+        <v>126963963</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6820,7 +6806,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6844,10 +6830,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524330</v>
+        <v>524305</v>
       </c>
       <c r="R50" t="n">
-        <v>6713764</v>
+        <v>6713787</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6859,7 +6845,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -6869,7 +6855,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Aspeboda</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6879,7 +6865,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6889,7 +6875,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6915,13 +6901,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126964000</t>
+          <t>https://artportalen.se/Sighting/126963963</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126964224</v>
+        <v>126964000</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6951,7 +6937,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6975,10 +6961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524279</v>
+        <v>524330</v>
       </c>
       <c r="R51" t="n">
-        <v>6713844</v>
+        <v>6713764</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6990,7 +6976,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -7000,7 +6986,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Aspeboda</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -7010,7 +6996,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7020,7 +7006,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7046,13 +7032,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126964224</t>
+          <t>https://artportalen.se/Sighting/126964000</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126964244</v>
+        <v>126964224</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -7106,7 +7092,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524280</v>
+        <v>524279</v>
       </c>
       <c r="R52" t="n">
         <v>6713844</v>
@@ -7141,7 +7127,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7151,7 +7137,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7177,13 +7163,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126964244</t>
+          <t>https://artportalen.se/Sighting/126964224</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127727522</v>
+        <v>126964244</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -7213,7 +7199,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7226,16 +7212,21 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524245</v>
+        <v>524280</v>
       </c>
       <c r="R53" t="n">
-        <v>6713763</v>
+        <v>6713844</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7262,22 +7253,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7303,13 +7294,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127727522</t>
+          <t>https://artportalen.se/Sighting/126964244</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129114973</v>
+        <v>127727522</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -7349,22 +7340,22 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524137</v>
+        <v>524245</v>
       </c>
       <c r="R54" t="n">
-        <v>6713729</v>
+        <v>6713763</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7388,22 +7379,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7429,16 +7420,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129114973</t>
+          <t>https://artportalen.se/Sighting/127727522</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131851232</v>
+        <v>129114973</v>
       </c>
       <c r="B55" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7475,19 +7466,19 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524414</v>
+        <v>524137</v>
       </c>
       <c r="R55" t="n">
-        <v>6713448</v>
+        <v>6713729</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7514,27 +7505,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ett 20tal bladrosetter.</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7560,13 +7546,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131851232</t>
+          <t>https://artportalen.se/Sighting/129114973</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131851767</v>
+        <v>131851232</v>
       </c>
       <c r="B56" t="n">
         <v>99195</v>
@@ -7596,17 +7582,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7615,10 +7601,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524422</v>
+        <v>524414</v>
       </c>
       <c r="R56" t="n">
-        <v>6713518</v>
+        <v>6713448</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7650,7 +7636,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7660,7 +7646,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ett 20tal bladrosetter.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7686,48 +7677,53 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131851767</t>
+          <t>https://artportalen.se/Sighting/131851232</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124034082</v>
+        <v>131851767</v>
       </c>
       <c r="B57" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7736,13 +7732,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524283</v>
+        <v>524422</v>
       </c>
       <c r="R57" t="n">
-        <v>6713661</v>
+        <v>6713518</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7766,22 +7762,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7806,6 +7802,127 @@
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851767</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>124034082</v>
+      </c>
+      <c r="B58" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>524283</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6713661</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124034082</t>
         </is>
@@ -7869,6 +7986,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>136991757</v>
       </c>
       <c r="B11" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>136991757</v>
       </c>
       <c r="B11" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -1775,11 +1775,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Smedsbo, Dlr</t>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>136991757</v>
       </c>
       <c r="B11" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>136991757</v>
       </c>
       <c r="B11" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>136991757</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>136991757</v>
       </c>
       <c r="B11" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
